--- a/Дело3а-78-2026Таганай/11_Поставщики/2. ИП Мамедов Фариз (мойка)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/2. ИП Мамедов Фариз (мойка)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92540505157</v>
+        <v>46157.93114787669</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/2. ИП Мамедов Фариз (мойка)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/2. ИП Мамедов Фариз (мойка)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93114787669</v>
+        <v>46157.93368628879</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/2. ИП Мамедов Фариз (мойка)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/2. ИП Мамедов Фариз (мойка)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93368628879</v>
+        <v>46157.93672603356</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/2. ИП Мамедов Фариз (мойка)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/2. ИП Мамедов Фариз (мойка)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93672603356</v>
+        <v>46158.28194661356</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/2. ИП Мамедов Фариз (мойка)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/2. ИП Мамедов Фариз (мойка)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28194661356</v>
+        <v>46158.29718781872</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/2. ИП Мамедов Фариз (мойка)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/2. ИП Мамедов Фариз (мойка)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29718781872</v>
+        <v>46158.29790804986</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/2. ИП Мамедов Фариз (мойка)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/2. ИП Мамедов Фариз (мойка)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29790804986</v>
+        <v>46158.33356192026</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/2. ИП Мамедов Фариз (мойка)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/2. ИП Мамедов Фариз (мойка)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33356192026</v>
+        <v>46158.37210897526</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/2. ИП Мамедов Фариз (мойка)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/2. ИП Мамедов Фариз (мойка)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.37210897526</v>
+        <v>46158.37267874935</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
